--- a/Config/Excel/BattlePlayer@玩家配置/BattlePlayer@cs.xlsx
+++ b/Config/Excel/BattlePlayer@玩家配置/BattlePlayer@cs.xlsx
@@ -1000,7 +1000,6 @@
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1037,7 +1036,7 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="F6" s="2"/>
     </row>
